--- a/public/demos/re-developer/draw-package.xlsx
+++ b/public/demos/re-developer/draw-package.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>The Madison at Riverside</t>
+          <t>Meridian Heights</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2400 Riverside Drive, Detroit, MI 48207</t>
+          <t>4500 Meridian Parkway, Columbus, OH 43215</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Riverside Development Partners LLC</t>
+          <t>Tangent Meridian Heights LLC</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>First National Construction Lending</t>
+          <t>Huntington National Bank — Construction Lending</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>CL-2025-0847</t>
+          <t>CL-2026-1247</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Riverside Builders Inc</t>
+          <t>Elford Construction</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Hamilton Design Associates</t>
+          <t>Moody Nolan Architects</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -963,7 +963,7 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>1404 Labs</t>
+          <t>Tangent Development</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>38500000</v>
+        <v>44200000</v>
       </c>
     </row>
     <row r="5">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>SUMIF('Change Order Log'!H2:H4,"approved",'Change Order Log'!E2:E4)</f>
+        <f>SUMIF('Change Order Log'!H2:H5,"approved",'Change Order Log'!E2:E5)</f>
         <v/>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>'G703'!G28</f>
+        <f>'G703'!G30</f>
         <v/>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>('G703'!D28+'G703'!E28)*0.1</f>
+        <f>('G703'!D30+'G703'!E30)*0.1</f>
         <v/>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>'G703'!F28*0.1</f>
+        <f>'G703'!F30*0.1</f>
         <v/>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>17842500</v>
+        <v>20850000</v>
       </c>
     </row>
     <row r="13">
@@ -1168,7 +1168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>2850000</v>
+        <v>2450000</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>2850000</v>
+        <v>2450000</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>0</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>5200000</v>
+        <v>4800000</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>5200000</v>
+        <v>4800000</v>
       </c>
       <c r="E4" s="13" t="n">
         <v>0</v>
@@ -1334,25 +1334,25 @@
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>05000</t>
+          <t>04000</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Structural Steel &amp; Metals</t>
+          <t>Masonry</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>4100000</v>
+        <v>1250000</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>3690000</v>
+        <v>875000</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>410000</v>
+        <v>250000</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0</v>
+        <v>62500</v>
       </c>
       <c r="G5" s="7">
         <f>D5+E5+F5</f>
@@ -1370,25 +1370,25 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>06000</t>
+          <t>05000</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Rough Carpentry &amp; Framing</t>
+          <t>Structural Steel &amp; Metals</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>3800000</v>
+        <v>3600000</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>2280000</v>
+        <v>3240000</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>570000</v>
+        <v>360000</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="G6" s="7">
         <f>D6+E6+F6</f>
@@ -1406,25 +1406,25 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>07000</t>
+          <t>06000</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Thermal &amp; Moisture Protection</t>
+          <t>Rough Carpentry &amp; Framing</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>2200000</v>
+        <v>4200000</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>880000</v>
+        <v>2520000</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>440000</v>
+        <v>630000</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>110000</v>
+        <v>210000</v>
       </c>
       <c r="G7" s="7">
         <f>D7+E7+F7</f>
@@ -1442,25 +1442,25 @@
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>08000</t>
+          <t>07000</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Doors, Windows &amp; Glazing</t>
+          <t>Thermal &amp; Moisture Protection</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>2600000</v>
+        <v>2400000</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>520000</v>
+        <v>960000</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>390000</v>
+        <v>480000</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>260000</v>
+        <v>120000</v>
       </c>
       <c r="G8" s="7">
         <f>D8+E8+F8</f>
@@ -1478,25 +1478,25 @@
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>09000</t>
+          <t>08000</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Finishes (Drywall, Paint, Flooring, Tile)</t>
+          <t>Doors, Windows &amp; Glazing</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>4500000</v>
+        <v>2800000</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>450000</v>
+        <v>560000</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>675000</v>
+        <v>420000</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>225000</v>
+        <v>280000</v>
       </c>
       <c r="G9" s="7">
         <f>D9+E9+F9</f>
@@ -1514,25 +1514,25 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>09000</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Mechanical / HVAC</t>
+          <t>Finishes (Drywall, Paint, Flooring, Tile)</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>3400000</v>
+        <v>5100000</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1360000</v>
+        <v>510000</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>510000</v>
+        <v>765000</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>170000</v>
+        <v>255000</v>
       </c>
       <c r="G10" s="7">
         <f>D10+E10+F10</f>
@@ -1550,25 +1550,25 @@
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Mechanical / HVAC</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>2100000</v>
+        <v>3800000</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1050000</v>
+        <v>1520000</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>315000</v>
+        <v>570000</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="G11" s="7">
         <f>D11+E11+F11</f>
@@ -1586,25 +1586,25 @@
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>2800000</v>
+        <v>2350000</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1120000</v>
+        <v>1175000</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>420000</v>
+        <v>352500</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>140000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="7">
         <f>D12+E12+F12</f>
@@ -1622,25 +1622,25 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>950000</v>
+        <v>3100000</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>285000</v>
+        <v>1240000</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>142500</v>
+        <v>465000</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0</v>
+        <v>155000</v>
       </c>
       <c r="G13" s="7">
         <f>D13+E13+F13</f>
@@ -1658,22 +1658,22 @@
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>32000</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Exterior Improvements &amp; Landscaping</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1200000</v>
+        <v>1050000</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>0</v>
+        <v>315000</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>0</v>
+        <v>157500</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>0</v>
@@ -1692,39 +1692,60 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SOFT COSTS</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>26000</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Elevator Installation</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>850000</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>170000</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>127500</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>85000</v>
+      </c>
+      <c r="G15" s="7">
+        <f>D15+E15+F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="19">
+        <f>IF(C15=0,0,G15/C15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="7">
+        <f>C15-G15</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Architecture &amp; Engineering</t>
+          <t>Exterior Improvements &amp; Landscaping</t>
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1800000</v>
+        <v>1350000</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1620000</v>
+        <v>0</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>0</v>
@@ -1743,60 +1764,39 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>S-02</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Permits &amp; Impact Fees</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>950000</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>950000</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7">
-        <f>D17+E17+F17</f>
-        <v/>
-      </c>
-      <c r="H17" s="19">
-        <f>IF(C17=0,0,G17/C17)</f>
-        <v/>
-      </c>
-      <c r="I17" s="7">
-        <f>C17-G17</f>
-        <v/>
-      </c>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SOFT COSTS</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>S-03</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Legal &amp; Title</t>
+          <t>Architecture &amp; Engineering</t>
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>350000</v>
+        <v>2350000</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>280000</v>
+        <v>2115000</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>35000</v>
+        <v>117500</v>
       </c>
       <c r="F18" s="13" t="n">
         <v>0</v>
@@ -1817,22 +1817,22 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Builder's Risk Insurance</t>
+          <t>Permits &amp; Impact Fees</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>425000</v>
+        <v>1400000</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>297500</v>
+        <v>1400000</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>42500</v>
+        <v>0</v>
       </c>
       <c r="F19" s="13" t="n">
         <v>0</v>
@@ -1851,39 +1851,60 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>FINANCING COSTS</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>S-03</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Legal &amp; Title</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>380000</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>304000</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>38000</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7">
+        <f>D20+E20+F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="19">
+        <f>IF(C20=0,0,G20/C20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="7">
+        <f>C20-G20</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Loan Origination &amp; Fees</t>
+          <t>Builder's Risk Insurance</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>575000</v>
+        <v>310000</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>575000</v>
+        <v>217000</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>0</v>
@@ -1902,139 +1923,118 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>FINANCING COSTS</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Loan Origination &amp; Fees</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>442000</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>442000</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7">
+        <f>D23+E23+F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="19">
+        <f>IF(C23=0,0,G23/C23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="7">
+        <f>C23-G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>F-02</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Capitalized Interest</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>1020000</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>121500</v>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="7">
-        <f>D22+E22+F22</f>
-        <v/>
-      </c>
-      <c r="H22" s="19">
-        <f>IF(C22=0,0,G22/C22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="7">
-        <f>C22-G22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="6" customHeight="1"/>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr"/>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>HARD COSTS SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C24" s="14">
-        <f>C3+C4+C5+C6+C7+C8+C9+C10+C11+C12+C13+C14</f>
-        <v/>
-      </c>
-      <c r="D24" s="14">
-        <f>D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14</f>
-        <v/>
-      </c>
-      <c r="E24" s="14">
-        <f>E3+E4+E5+E6+E7+E8+E9+E10+E11+E12+E13+E14</f>
-        <v/>
-      </c>
-      <c r="F24" s="14">
-        <f>F3+F4+F5+F6+F7+F8+F9+F10+F11+F12+F13+F14</f>
-        <v/>
-      </c>
-      <c r="G24" s="14">
-        <f>G3+G4+G5+G6+G7+G8+G9+G10+G11+G12+G13+G14</f>
-        <v/>
-      </c>
-      <c r="H24" s="22">
+      <c r="C24" s="13" t="n">
+        <v>2020000</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>1212000</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>141750</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7">
+        <f>D24+E24+F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="19">
         <f>IF(C24=0,0,G24/C24)</f>
         <v/>
       </c>
-      <c r="I24" s="14">
-        <f>I3+I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr"/>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>SOFT COSTS SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C25" s="14">
-        <f>C16+C17+C18+C19</f>
-        <v/>
-      </c>
-      <c r="D25" s="14">
-        <f>D16+D17+D18+D19</f>
-        <v/>
-      </c>
-      <c r="E25" s="14">
-        <f>E16+E17+E18+E19</f>
-        <v/>
-      </c>
-      <c r="F25" s="14">
-        <f>F16+F17+F18+F19</f>
-        <v/>
-      </c>
-      <c r="G25" s="14">
-        <f>G16+G17+G18+G19</f>
-        <v/>
-      </c>
-      <c r="H25" s="22">
-        <f>IF(C25=0,0,G25/C25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="14">
-        <f>I16+I17+I18+I19</f>
-        <v/>
-      </c>
-    </row>
+      <c r="I24" s="7">
+        <f>C24-G24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
     <row r="26">
       <c r="A26" s="20" t="inlineStr"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>FINANCING COSTS SUBTOTAL</t>
+          <t>HARD COSTS SUBTOTAL</t>
         </is>
       </c>
       <c r="C26" s="14">
-        <f>C21+C22</f>
+        <f>C3+C4+C5+C6+C7+C8+C9+C10+C11+C12+C13+C14+C15+C16</f>
         <v/>
       </c>
       <c r="D26" s="14">
-        <f>D21+D22</f>
+        <f>D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
         <v/>
       </c>
       <c r="E26" s="14">
-        <f>E21+E22</f>
+        <f>E3+E4+E5+E6+E7+E8+E9+E10+E11+E12+E13+E14+E15+E16</f>
         <v/>
       </c>
       <c r="F26" s="14">
-        <f>F21+F22</f>
+        <f>F3+F4+F5+F6+F7+F8+F9+F10+F11+F12+F13+F14+F15+F16</f>
         <v/>
       </c>
       <c r="G26" s="14">
-        <f>G21+G22</f>
+        <f>G3+G4+G5+G6+G7+G8+G9+G10+G11+G12+G13+G14+G15+G16</f>
         <v/>
       </c>
       <c r="H26" s="22">
@@ -2042,49 +2042,121 @@
         <v/>
       </c>
       <c r="I26" s="14">
-        <f>I21+I22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="6" customHeight="1"/>
+        <f>I3+I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr"/>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>SOFT COSTS SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C27" s="14">
+        <f>C18+C19+C20+C21</f>
+        <v/>
+      </c>
+      <c r="D27" s="14">
+        <f>D18+D19+D20+D21</f>
+        <v/>
+      </c>
+      <c r="E27" s="14">
+        <f>E18+E19+E20+E21</f>
+        <v/>
+      </c>
+      <c r="F27" s="14">
+        <f>F18+F19+F20+F21</f>
+        <v/>
+      </c>
+      <c r="G27" s="14">
+        <f>G18+G19+G20+G21</f>
+        <v/>
+      </c>
+      <c r="H27" s="22">
+        <f>IF(C27=0,0,G27/C27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="14">
+        <f>I18+I19+I20+I21</f>
+        <v/>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr"/>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr"/>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>FINANCING COSTS SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C28" s="14">
+        <f>C23+C24</f>
+        <v/>
+      </c>
+      <c r="D28" s="14">
+        <f>D23+D24</f>
+        <v/>
+      </c>
+      <c r="E28" s="14">
+        <f>E23+E24</f>
+        <v/>
+      </c>
+      <c r="F28" s="14">
+        <f>F23+F24</f>
+        <v/>
+      </c>
+      <c r="G28" s="14">
+        <f>G23+G24</f>
+        <v/>
+      </c>
+      <c r="H28" s="22">
+        <f>IF(C28=0,0,G28/C28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="14">
+        <f>I23+I24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="6" customHeight="1"/>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr"/>
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="C28" s="25">
-        <f>C24+C25+C26</f>
-        <v/>
-      </c>
-      <c r="D28" s="25">
-        <f>D24+D25+D26</f>
-        <v/>
-      </c>
-      <c r="E28" s="25">
-        <f>E24+E25+E26</f>
-        <v/>
-      </c>
-      <c r="F28" s="25">
-        <f>F24+F25+F26</f>
-        <v/>
-      </c>
-      <c r="G28" s="25">
-        <f>G24+G25+G26</f>
-        <v/>
-      </c>
-      <c r="H28" s="26">
-        <f>IF(C28=0,0,G28/C28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="25">
-        <f>I24+I25+I26</f>
+      <c r="C30" s="25">
+        <f>C26+C27+C28</f>
+        <v/>
+      </c>
+      <c r="D30" s="25">
+        <f>D26+D27+D28</f>
+        <v/>
+      </c>
+      <c r="E30" s="25">
+        <f>E26+E27+E28</f>
+        <v/>
+      </c>
+      <c r="F30" s="25">
+        <f>F26+F27+F28</f>
+        <v/>
+      </c>
+      <c r="G30" s="25">
+        <f>G26+G27+G28</f>
+        <v/>
+      </c>
+      <c r="H30" s="26">
+        <f>IF(C30=0,0,G30/C30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="25">
+        <f>I26+I27+I28</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H22">
+  <conditionalFormatting sqref="H2:H24">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.999</formula>
     </cfRule>
@@ -2104,7 +2176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2168,21 +2240,21 @@
       </c>
       <c r="B2" s="18" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Upgraded elevator cab finishes per owner request</t>
+          <t>Enhanced lobby finishes and upgraded amenity package per ownership directive</t>
         </is>
       </c>
       <c r="E2" s="13" t="n">
-        <v>185000</v>
+        <v>215000</v>
       </c>
       <c r="F2" s="7">
         <f>E2</f>
@@ -2203,28 +2275,28 @@
       </c>
       <c r="B3" s="18" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Rock removal — unforeseen subsurface conditions at Building C</t>
+          <t>Dewatering system for unexpected high water table at podium level</t>
         </is>
       </c>
       <c r="E3" s="13" t="n">
-        <v>342000</v>
+        <v>287000</v>
       </c>
       <c r="F3" s="7">
         <f>F2+E3</f>
         <v/>
       </c>
       <c r="G3" s="27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H3" s="18" t="inlineStr">
         <is>
@@ -2238,28 +2310,28 @@
       </c>
       <c r="B4" s="18" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Structural steel reinforcement per revised wind load calcs</t>
+          <t>Upgraded fire alarm panel to addressable system per city code revision</t>
         </is>
       </c>
       <c r="E4" s="13" t="n">
-        <v>128000</v>
+        <v>94000</v>
       </c>
       <c r="F4" s="7">
         <f>F3+E4</f>
         <v/>
       </c>
       <c r="G4" s="27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H4" s="18" t="inlineStr">
         <is>
@@ -2267,28 +2339,59 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1"/>
-    <row r="6">
-      <c r="B6" s="24" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>EV charging infrastructure for 40 parking spaces per revised ESG commitment</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>168000</v>
+      </c>
+      <c r="F5" s="7">
+        <f>F4+E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="6" customHeight="1"/>
+    <row r="7">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="E6" s="25">
-        <f>SUM(E2:E4)</f>
-        <v/>
-      </c>
-      <c r="F6" s="25">
-        <f>F4</f>
-        <v/>
-      </c>
-      <c r="G6" s="28">
-        <f>SUM(G2:G4)</f>
+      <c r="E7" s="25">
+        <f>SUM(E2:E5)</f>
+        <v/>
+      </c>
+      <c r="F7" s="25">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="G7" s="28">
+        <f>SUM(G2:G5)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="H2:H5">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"approved"</formula>
     </cfRule>
@@ -2311,7 +2414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2408,7 +2511,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>2850000</v>
+        <v>2450000</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>0</v>
@@ -2418,7 +2521,7 @@
         <v/>
       </c>
       <c r="E3" s="13" t="n">
-        <v>2850000</v>
+        <v>2450000</v>
       </c>
       <c r="F3" s="13" t="n">
         <v>0</v>
@@ -2447,7 +2550,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>5200000</v>
+        <v>4800000</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>0</v>
@@ -2457,7 +2560,7 @@
         <v/>
       </c>
       <c r="E4" s="13" t="n">
-        <v>5200000</v>
+        <v>4800000</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>0</v>
@@ -2482,11 +2585,11 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Structural Steel &amp; Metals</t>
+          <t>Masonry</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>4100000</v>
+        <v>1250000</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>0</v>
@@ -2496,10 +2599,10 @@
         <v/>
       </c>
       <c r="E5" s="13" t="n">
-        <v>3690000</v>
+        <v>875000</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>410000</v>
+        <v>312500</v>
       </c>
       <c r="G5" s="7">
         <f>E5+F5</f>
@@ -2521,11 +2624,11 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Rough Carpentry &amp; Framing</t>
+          <t>Structural Steel &amp; Metals</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>3800000</v>
+        <v>3600000</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>0</v>
@@ -2535,10 +2638,10 @@
         <v/>
       </c>
       <c r="E6" s="13" t="n">
-        <v>2280000</v>
+        <v>3240000</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>760000</v>
+        <v>360000</v>
       </c>
       <c r="G6" s="7">
         <f>E6+F6</f>
@@ -2560,11 +2663,11 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Thermal &amp; Moisture Protection</t>
+          <t>Rough Carpentry &amp; Framing</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>2200000</v>
+        <v>4200000</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>0</v>
@@ -2574,10 +2677,10 @@
         <v/>
       </c>
       <c r="E7" s="13" t="n">
-        <v>880000</v>
+        <v>2520000</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>550000</v>
+        <v>840000</v>
       </c>
       <c r="G7" s="7">
         <f>E7+F7</f>
@@ -2599,11 +2702,11 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Doors, Windows &amp; Glazing</t>
+          <t>Thermal &amp; Moisture Protection</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>2600000</v>
+        <v>2400000</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>0</v>
@@ -2613,10 +2716,10 @@
         <v/>
       </c>
       <c r="E8" s="13" t="n">
-        <v>520000</v>
+        <v>960000</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="G8" s="7">
         <f>E8+F8</f>
@@ -2638,11 +2741,11 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Finishes (Drywall, Paint, Flooring, Tile)</t>
+          <t>Doors, Windows &amp; Glazing</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>4500000</v>
+        <v>2800000</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>0</v>
@@ -2652,10 +2755,10 @@
         <v/>
       </c>
       <c r="E9" s="13" t="n">
-        <v>450000</v>
+        <v>560000</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>900000</v>
+        <v>700000</v>
       </c>
       <c r="G9" s="7">
         <f>E9+F9</f>
@@ -2677,11 +2780,11 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Mechanical / HVAC</t>
+          <t>Finishes (Drywall, Paint, Flooring, Tile)</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>3400000</v>
+        <v>5100000</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>0</v>
@@ -2691,10 +2794,10 @@
         <v/>
       </c>
       <c r="E10" s="13" t="n">
-        <v>1360000</v>
+        <v>510000</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>680000</v>
+        <v>1020000</v>
       </c>
       <c r="G10" s="7">
         <f>E10+F10</f>
@@ -2716,11 +2819,11 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Mechanical / HVAC</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>2100000</v>
+        <v>3800000</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>0</v>
@@ -2730,10 +2833,10 @@
         <v/>
       </c>
       <c r="E11" s="13" t="n">
-        <v>1050000</v>
+        <v>1520000</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>315000</v>
+        <v>760000</v>
       </c>
       <c r="G11" s="7">
         <f>E11+F11</f>
@@ -2755,11 +2858,11 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>2800000</v>
+        <v>2350000</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>0</v>
@@ -2769,10 +2872,10 @@
         <v/>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1120000</v>
+        <v>1175000</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>560000</v>
+        <v>352500</v>
       </c>
       <c r="G12" s="7">
         <f>E12+F12</f>
@@ -2794,11 +2897,11 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>950000</v>
+        <v>3100000</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>0</v>
@@ -2808,10 +2911,10 @@
         <v/>
       </c>
       <c r="E13" s="13" t="n">
-        <v>285000</v>
+        <v>1240000</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>142500</v>
+        <v>620000</v>
       </c>
       <c r="G13" s="7">
         <f>E13+F13</f>
@@ -2833,11 +2936,11 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Exterior Improvements &amp; Landscaping</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1200000</v>
+        <v>1050000</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>0</v>
@@ -2847,10 +2950,10 @@
         <v/>
       </c>
       <c r="E14" s="13" t="n">
-        <v>0</v>
+        <v>315000</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0</v>
+        <v>157500</v>
       </c>
       <c r="G14" s="7">
         <f>E14+F14</f>
@@ -2870,29 +2973,52 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SOFT COSTS</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Elevator Installation</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>850000</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7">
+        <f>B15+C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>170000</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>212500</v>
+      </c>
+      <c r="G15" s="7">
+        <f>E15+F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="7">
+        <f>D15-G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="13">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="J15" s="7">
+        <f>I15-D15</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Architecture &amp; Engineering</t>
+          <t>Exterior Improvements &amp; Landscaping</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1800000</v>
+        <v>1350000</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>0</v>
@@ -2902,10 +3028,10 @@
         <v/>
       </c>
       <c r="E16" s="13" t="n">
-        <v>1620000</v>
+        <v>0</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="G16" s="7">
         <f>E16+F16</f>
@@ -2925,52 +3051,29 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Permits &amp; Impact Fees</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>950000</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7">
-        <f>B17+C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>950000</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7">
-        <f>E17+F17</f>
-        <v/>
-      </c>
-      <c r="H17" s="7">
-        <f>D17-G17</f>
-        <v/>
-      </c>
-      <c r="I17" s="13">
-        <f>D17</f>
-        <v/>
-      </c>
-      <c r="J17" s="7">
-        <f>I17-D17</f>
-        <v/>
-      </c>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SOFT COSTS</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Legal &amp; Title</t>
+          <t>Architecture &amp; Engineering</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>350000</v>
+        <v>2350000</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>0</v>
@@ -2980,10 +3083,10 @@
         <v/>
       </c>
       <c r="E18" s="13" t="n">
-        <v>280000</v>
+        <v>2115000</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>35000</v>
+        <v>117500</v>
       </c>
       <c r="G18" s="7">
         <f>E18+F18</f>
@@ -3005,11 +3108,11 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Builder's Risk Insurance</t>
+          <t>Permits &amp; Impact Fees</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>425000</v>
+        <v>1400000</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>0</v>
@@ -3019,10 +3122,10 @@
         <v/>
       </c>
       <c r="E19" s="13" t="n">
-        <v>297500</v>
+        <v>1400000</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>42500</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7">
         <f>E19+F19</f>
@@ -3042,29 +3145,52 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>FINANCING COSTS</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Legal &amp; Title</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>380000</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7">
+        <f>B20+C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>304000</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G20" s="7">
+        <f>E20+F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="7">
+        <f>D20-G20</f>
+        <v/>
+      </c>
+      <c r="I20" s="13">
+        <f>D20</f>
+        <v/>
+      </c>
+      <c r="J20" s="7">
+        <f>I20-D20</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Loan Origination &amp; Fees</t>
+          <t>Builder's Risk Insurance</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>575000</v>
+        <v>310000</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0</v>
@@ -3074,10 +3200,10 @@
         <v/>
       </c>
       <c r="E21" s="13" t="n">
-        <v>575000</v>
+        <v>217000</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="G21" s="7">
         <f>E21+F21</f>
@@ -3097,143 +3223,112 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>FINANCING COSTS</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Loan Origination &amp; Fees</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>442000</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="7">
+        <f>B23+C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>442000</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7">
+        <f>E23+F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="7">
+        <f>D23-G23</f>
+        <v/>
+      </c>
+      <c r="I23" s="13">
+        <f>D23</f>
+        <v/>
+      </c>
+      <c r="J23" s="7">
+        <f>I23-D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Capitalized Interest</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="C22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="7">
-        <f>B22+C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>1020000</v>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>121500</v>
-      </c>
-      <c r="G22" s="7">
-        <f>E22+F22</f>
-        <v/>
-      </c>
-      <c r="H22" s="7">
-        <f>D22-G22</f>
-        <v/>
-      </c>
-      <c r="I22" s="13">
-        <f>D22</f>
-        <v/>
-      </c>
-      <c r="J22" s="7">
-        <f>I22-D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="6" customHeight="1"/>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>HARD COSTS SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B24" s="14">
-        <f>B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14</f>
-        <v/>
-      </c>
-      <c r="C24" s="14">
-        <f>C3+C4+C5+C6+C7+C8+C9+C10+C11+C12+C13+C14</f>
-        <v/>
-      </c>
-      <c r="D24" s="14">
+      <c r="B24" s="13" t="n">
+        <v>2020000</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7">
         <f>B24+C24</f>
         <v/>
       </c>
-      <c r="E24" s="14">
-        <f>E3+E4+E5+E6+E7+E8+E9+E10+E11+E12+E13+E14</f>
-        <v/>
-      </c>
-      <c r="F24" s="14">
-        <f>F3+F4+F5+F6+F7+F8+F9+F10+F11+F12+F13+F14</f>
-        <v/>
-      </c>
-      <c r="G24" s="14">
+      <c r="E24" s="13" t="n">
+        <v>1212000</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>141750</v>
+      </c>
+      <c r="G24" s="7">
         <f>E24+F24</f>
         <v/>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="7">
         <f>D24-G24</f>
         <v/>
       </c>
-      <c r="I24" s="14">
-        <f>I3+I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14</f>
-        <v/>
-      </c>
-      <c r="J24" s="14">
+      <c r="I24" s="13">
+        <f>D24</f>
+        <v/>
+      </c>
+      <c r="J24" s="7">
         <f>I24-D24</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>SOFT COSTS SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="14">
-        <f>B16+B17+B18+B19</f>
-        <v/>
-      </c>
-      <c r="C25" s="14">
-        <f>C16+C17+C18+C19</f>
-        <v/>
-      </c>
-      <c r="D25" s="14">
-        <f>B25+C25</f>
-        <v/>
-      </c>
-      <c r="E25" s="14">
-        <f>E16+E17+E18+E19</f>
-        <v/>
-      </c>
-      <c r="F25" s="14">
-        <f>F16+F17+F18+F19</f>
-        <v/>
-      </c>
-      <c r="G25" s="14">
-        <f>E25+F25</f>
-        <v/>
-      </c>
-      <c r="H25" s="14">
-        <f>D25-G25</f>
-        <v/>
-      </c>
-      <c r="I25" s="14">
-        <f>I16+I17+I18+I19</f>
-        <v/>
-      </c>
-      <c r="J25" s="14">
-        <f>I25-D25</f>
-        <v/>
-      </c>
-    </row>
+    <row r="25" ht="6" customHeight="1"/>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>FINANCING COSTS SUBTOTAL</t>
+          <t>HARD COSTS SUBTOTAL</t>
         </is>
       </c>
       <c r="B26" s="14">
-        <f>B21+B22</f>
+        <f>B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16</f>
         <v/>
       </c>
       <c r="C26" s="14">
-        <f>C21+C22</f>
+        <f>C3+C4+C5+C6+C7+C8+C9+C10+C11+C12+C13+C14+C15+C16</f>
         <v/>
       </c>
       <c r="D26" s="14">
@@ -3241,11 +3336,11 @@
         <v/>
       </c>
       <c r="E26" s="14">
-        <f>E21+E22</f>
+        <f>E3+E4+E5+E6+E7+E8+E9+E10+E11+E12+E13+E14+E15+E16</f>
         <v/>
       </c>
       <c r="F26" s="14">
-        <f>F21+F22</f>
+        <f>F3+F4+F5+F6+F7+F8+F9+F10+F11+F12+F13+F14+F15+F16</f>
         <v/>
       </c>
       <c r="G26" s="14">
@@ -3257,7 +3352,7 @@
         <v/>
       </c>
       <c r="I26" s="14">
-        <f>I21+I22</f>
+        <f>I3+I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16</f>
         <v/>
       </c>
       <c r="J26" s="14">
@@ -3265,52 +3360,138 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="6" customHeight="1"/>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>SOFT COSTS SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B27" s="14">
+        <f>B18+B19+B20+B21</f>
+        <v/>
+      </c>
+      <c r="C27" s="14">
+        <f>C18+C19+C20+C21</f>
+        <v/>
+      </c>
+      <c r="D27" s="14">
+        <f>B27+C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="14">
+        <f>E18+E19+E20+E21</f>
+        <v/>
+      </c>
+      <c r="F27" s="14">
+        <f>F18+F19+F20+F21</f>
+        <v/>
+      </c>
+      <c r="G27" s="14">
+        <f>E27+F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="14">
+        <f>D27-G27</f>
+        <v/>
+      </c>
+      <c r="I27" s="14">
+        <f>I18+I19+I20+I21</f>
+        <v/>
+      </c>
+      <c r="J27" s="14">
+        <f>I27-D27</f>
+        <v/>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>FINANCING COSTS SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B28" s="14">
+        <f>B23+B24</f>
+        <v/>
+      </c>
+      <c r="C28" s="14">
+        <f>C23+C24</f>
+        <v/>
+      </c>
+      <c r="D28" s="14">
+        <f>B28+C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="14">
+        <f>E23+E24</f>
+        <v/>
+      </c>
+      <c r="F28" s="14">
+        <f>F23+F24</f>
+        <v/>
+      </c>
+      <c r="G28" s="14">
+        <f>E28+F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="14">
+        <f>D28-G28</f>
+        <v/>
+      </c>
+      <c r="I28" s="14">
+        <f>I23+I24</f>
+        <v/>
+      </c>
+      <c r="J28" s="14">
+        <f>I28-D28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="6" customHeight="1"/>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROJECT BUDGET</t>
         </is>
       </c>
-      <c r="B28" s="25">
-        <f>B24+B25+B26</f>
-        <v/>
-      </c>
-      <c r="C28" s="25">
-        <f>C24+C25+C26</f>
-        <v/>
-      </c>
-      <c r="D28" s="25">
-        <f>B28+C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="25">
-        <f>E24+E25+E26</f>
-        <v/>
-      </c>
-      <c r="F28" s="25">
-        <f>F24+F25+F26</f>
-        <v/>
-      </c>
-      <c r="G28" s="25">
-        <f>E28+F28</f>
-        <v/>
-      </c>
-      <c r="H28" s="25">
-        <f>D28-G28</f>
-        <v/>
-      </c>
-      <c r="I28" s="25">
-        <f>I24+I25+I26</f>
-        <v/>
-      </c>
-      <c r="J28" s="25">
-        <f>I28-D28</f>
+      <c r="B30" s="25">
+        <f>B26+B27+B28</f>
+        <v/>
+      </c>
+      <c r="C30" s="25">
+        <f>C26+C27+C28</f>
+        <v/>
+      </c>
+      <c r="D30" s="25">
+        <f>B30+C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="25">
+        <f>E26+E27+E28</f>
+        <v/>
+      </c>
+      <c r="F30" s="25">
+        <f>F26+F27+F28</f>
+        <v/>
+      </c>
+      <c r="G30" s="25">
+        <f>E30+F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="25">
+        <f>D30-G30</f>
+        <v/>
+      </c>
+      <c r="I30" s="25">
+        <f>I26+I27+I28</f>
+        <v/>
+      </c>
+      <c r="J30" s="25">
+        <f>I30-D30</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J3:J22">
+  <conditionalFormatting sqref="J3:J24">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -3330,7 +3511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3406,7 +3587,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Great Lakes Excavating</t>
+          <t>Central Ohio Earthworks</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -3415,10 +3596,10 @@
         </is>
       </c>
       <c r="C2" s="13" t="n">
-        <v>2850000</v>
+        <v>2450000</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>2565000</v>
+        <v>2205000</v>
       </c>
       <c r="E2" s="13" t="n">
         <v>0</v>
@@ -3451,19 +3632,19 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Motor City Concrete</t>
+          <t>Buckeye Concrete Inc</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Concrete &amp; Foundations</t>
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>5200000</v>
+        <v>4800000</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>4680000</v>
+        <v>4320000</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>0</v>
@@ -3484,7 +3665,7 @@
       </c>
       <c r="I3" s="18" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -3496,22 +3677,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Ironworkers Local 25 Steel</t>
+          <t>Capital City Masonry</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Masonry</t>
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>4100000</v>
+        <v>1250000</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>3321000</v>
+        <v>787500</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>369000</v>
+        <v>281250</v>
       </c>
       <c r="F4" s="7">
         <f>C4-D4-E4</f>
@@ -3537,22 +3718,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Midwest Framing Corp</t>
+          <t>Midwest Steel Erectors</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Rough Carpentry</t>
+          <t>Structural Steel</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>3800000</v>
+        <v>3600000</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>2052000</v>
+        <v>2916000</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>684000</v>
+        <v>324000</v>
       </c>
       <c r="F5" s="7">
         <f>C5-D5-E5</f>
@@ -3578,22 +3759,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Barrier Systems Inc</t>
+          <t>Scioto Framing Corp</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Waterproofing &amp; Insulation</t>
+          <t>Rough Carpentry</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>2200000</v>
+        <v>4200000</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>792000</v>
+        <v>2268000</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>495000</v>
+        <v>756000</v>
       </c>
       <c r="F6" s="7">
         <f>C6-D6-E6</f>
@@ -3606,7 +3787,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr">
@@ -3614,31 +3795,27 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>Unconditional for Draw 6 still pending</t>
-        </is>
-      </c>
+      <c r="J6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Wolverine Glass &amp; Glazing</t>
+          <t>Ohio Weatherproofing LLC</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Windows &amp; Glazing</t>
+          <t>Waterproofing &amp; Insulation</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>2600000</v>
+        <v>2400000</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>468000</v>
+        <v>864000</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>585000</v>
+        <v>540000</v>
       </c>
       <c r="F7" s="7">
         <f>C7-D7-E7</f>
@@ -3651,7 +3828,7 @@
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="I7" s="18" t="inlineStr">
@@ -3659,27 +3836,31 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Unconditional for Draw 7 still pending</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Elite Interior Finishes</t>
+          <t>Columbus Glass &amp; Curtainwall</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Windows &amp; Glazing</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>4500000</v>
+        <v>2800000</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>405000</v>
+        <v>504000</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>810000</v>
+        <v>630000</v>
       </c>
       <c r="F8" s="7">
         <f>C8-D8-E8</f>
@@ -3687,7 +3868,7 @@
       </c>
       <c r="G8" s="18" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="H8" s="18" t="inlineStr">
@@ -3695,32 +3876,32 @@
           <t>Received</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>Conditional waiver requested — awaiting return</t>
-        </is>
-      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Comfort Mechanical</t>
+          <t>Premier Interior Solutions</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>3400000</v>
+        <v>5100000</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1224000</v>
+        <v>459000</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>612000</v>
+        <v>918000</v>
       </c>
       <c r="F9" s="7">
         <f>C9-D9-E9</f>
@@ -3728,40 +3909,40 @@
       </c>
       <c r="G9" s="18" t="inlineStr">
         <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr"/>
+      <c r="I9" s="18" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Conditional waiver requested — awaiting return</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Allied Plumbing Services</t>
+          <t>Heartland Mechanical</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>2100000</v>
+        <v>3800000</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>945000</v>
+        <v>1368000</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>283500</v>
+        <v>684000</v>
       </c>
       <c r="F10" s="7">
         <f>C10-D10-E10</f>
@@ -3779,7 +3960,7 @@
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
@@ -3787,22 +3968,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>PowerLine Electric</t>
+          <t>Olentangy Plumbing Services</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>2800000</v>
+        <v>2350000</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1008000</v>
+        <v>1057500</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>504000</v>
+        <v>317250</v>
       </c>
       <c r="F11" s="7">
         <f>C11-D11-E11</f>
@@ -3815,39 +3996,35 @@
       </c>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>Unconditional for Draw 6 missing — follow up</t>
-        </is>
-      </c>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>FireGuard Sprinkler</t>
+          <t>Apex Electrical Contractors</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>950000</v>
+        <v>3100000</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>256500</v>
+        <v>1116000</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>128250</v>
+        <v>558000</v>
       </c>
       <c r="F12" s="7">
         <f>C12-D12-E12</f>
@@ -3860,35 +4037,39 @@
       </c>
       <c r="H12" s="18" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr"/>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Unconditional for Draw 7 missing — follow up</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>GreenScape Landscaping</t>
+          <t>Buckeye Fire Protection</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1200000</v>
+        <v>1050000</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>0</v>
+        <v>283500</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>0</v>
+        <v>141750</v>
       </c>
       <c r="F13" s="7">
         <f>C13-D13-E13</f>
@@ -3896,142 +4077,224 @@
       </c>
       <c r="G13" s="18" t="inlineStr">
         <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Schindler Elevator Corp</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Elevators</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>850000</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>153000</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>191250</v>
+      </c>
+      <c r="F14" s="7">
+        <f>C14-D14-E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Greenview Landscaping</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Landscaping &amp; Exterior</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7">
+        <f>C15-D15-E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I13" s="18" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>Not yet mobilized</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="6" customHeight="1"/>
-    <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+    <row r="16" ht="6" customHeight="1"/>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="C15" s="25">
-        <f>SUM(C2:C13)</f>
-        <v/>
-      </c>
-      <c r="D15" s="25">
-        <f>SUM(D2:D13)</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>SUM(E2:E13)</f>
-        <v/>
-      </c>
-      <c r="F15" s="25">
-        <f>SUM(F2:F13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="C17" s="25">
+        <f>SUM(C2:C15)</f>
+        <v/>
+      </c>
+      <c r="D17" s="25">
+        <f>SUM(D2:D15)</f>
+        <v/>
+      </c>
+      <c r="E17" s="25">
+        <f>SUM(E2:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="25">
+        <f>SUM(F2:F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>COMPLIANCE SUMMARY</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Active Subcontractors</t>
-        </is>
-      </c>
-      <c r="B18" s="30">
-        <f>COUNTIF(E2:E13,"&gt;0")+COUNTIF(D2:D13,"&gt;0")-COUNTIFS(E2:E13,"&gt;0",D2:D13,"&gt;0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Conditional Waivers — Received</t>
-        </is>
-      </c>
-      <c r="B19" s="30">
-        <f>COUNTIF(G2:G13,"Received")</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Conditional Waivers — Pending</t>
+          <t>Active Subcontractors</t>
         </is>
       </c>
       <c r="B20" s="30">
-        <f>COUNTIF(G2:G13,"Pending")</f>
+        <f>COUNTIF(E2:E15,"&gt;0")+COUNTIF(D2:D15,"&gt;0")-COUNTIFS(E2:E15,"&gt;0",D2:D15,"&gt;0")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Conditional Waivers — Missing</t>
+          <t>Conditional Waivers — Received</t>
         </is>
       </c>
       <c r="B21" s="30">
-        <f>COUNTIF(G2:G13,"Missing")</f>
+        <f>COUNTIF(G2:G15,"Received")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Unconditional Waivers — Received</t>
+          <t>Conditional Waivers — Pending</t>
         </is>
       </c>
       <c r="B22" s="30">
-        <f>COUNTIF(H2:H13,"Received")</f>
+        <f>COUNTIF(G2:G15,"Pending")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Unconditional Waivers — Pending/Missing</t>
+          <t>Conditional Waivers — Missing</t>
         </is>
       </c>
       <c r="B23" s="30">
-        <f>COUNTIF(H2:H13,"Pending")+COUNTIF(H2:H13,"Missing")</f>
+        <f>COUNTIF(G2:G15,"Missing")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Unconditional Waivers — Received</t>
+        </is>
+      </c>
+      <c r="B24" s="30">
+        <f>COUNTIF(H2:H15,"Received")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>Unconditional Waivers — Pending/Missing</t>
+        </is>
+      </c>
+      <c r="B25" s="30">
+        <f>COUNTIF(H2:H15,"Pending")+COUNTIF(H2:H15,"Missing")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>Conditional Compliance %</t>
         </is>
       </c>
-      <c r="B25" s="31">
-        <f>IF((COUNTIF(G2:G13,"Received")+COUNTIF(G2:G13,"Pending")+COUNTIF(G2:G13,"Missing"))=0,0,COUNTIF(G2:G13,"Received")/(COUNTIF(G2:G13,"Received")+COUNTIF(G2:G13,"Pending")+COUNTIF(G2:G13,"Missing")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="B27" s="31">
+        <f>IF((COUNTIF(G2:G15,"Received")+COUNTIF(G2:G15,"Pending")+COUNTIF(G2:G15,"Missing"))=0,0,COUNTIF(G2:G15,"Received")/(COUNTIF(G2:G15,"Received")+COUNTIF(G2:G15,"Pending")+COUNTIF(G2:G15,"Missing")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Unconditional Compliance %</t>
         </is>
       </c>
-      <c r="B26" s="31">
-        <f>IF((COUNTIF(H2:H13,"Received")+COUNTIF(H2:H13,"Pending")+COUNTIF(H2:H13,"Missing"))=0,0,COUNTIF(H2:H13,"Received")/(COUNTIF(H2:H13,"Received")+COUNTIF(H2:H13,"Pending")+COUNTIF(H2:H13,"Missing")))</f>
+      <c r="B28" s="31">
+        <f>IF((COUNTIF(H2:H15,"Received")+COUNTIF(H2:H15,"Pending")+COUNTIF(H2:H15,"Missing"))=0,0,COUNTIF(H2:H15,"Received")/(COUNTIF(H2:H15,"Received")+COUNTIF(H2:H15,"Pending")+COUNTIF(H2:H15,"Missing")))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G2:G15">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Received"</formula>
     </cfRule>
@@ -4042,7 +4305,7 @@
       <formula>"Missing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H13">
+  <conditionalFormatting sqref="H2:H15">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
       <formula>"Received"</formula>
     </cfRule>

--- a/public/demos/re-developer/draw-package.xlsx
+++ b/public/demos/re-developer/draw-package.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Meridian Heights</t>
+          <t>The Madison at Riverside</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4500 Meridian Parkway, Columbus, OH 43215</t>
+          <t>2400 Riverside Drive, Detroit, MI 48207</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Tangent Meridian Heights LLC</t>
+          <t>Riverside Development Partners LLC</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Huntington National Bank — Construction Lending</t>
+          <t>First National Construction Lending</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>CL-2026-1247</t>
+          <t>CL-2025-0847</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Elford Construction</t>
+          <t>Riverside Builders Inc</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Moody Nolan Architects</t>
+          <t>Hamilton Design Associates</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -963,7 +963,7 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Tangent Development</t>
+          <t>1404 Labs</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>44200000</v>
+        <v>38500000</v>
       </c>
     </row>
     <row r="5">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>SUMIF('Change Order Log'!H2:H5,"approved",'Change Order Log'!E2:E5)</f>
+        <f>SUMIF('Change Order Log'!H2:H4,"approved",'Change Order Log'!E2:E4)</f>
         <v/>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>'G703'!G30</f>
+        <f>'G703'!G28</f>
         <v/>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>('G703'!D30+'G703'!E30)*0.1</f>
+        <f>('G703'!D28+'G703'!E28)*0.1</f>
         <v/>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>'G703'!F30*0.1</f>
+        <f>'G703'!F28*0.1</f>
         <v/>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>20850000</v>
+        <v>17842500</v>
       </c>
     </row>
     <row r="13">
@@ -1168,7 +1168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>2450000</v>
+        <v>2850000</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>2450000</v>
+        <v>2850000</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>0</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>4800000</v>
+        <v>5200000</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>4800000</v>
+        <v>5200000</v>
       </c>
       <c r="E4" s="13" t="n">
         <v>0</v>
@@ -1334,25 +1334,25 @@
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>04000</t>
+          <t>05000</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Masonry</t>
+          <t>Structural Steel &amp; Metals</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1250000</v>
+        <v>4100000</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>875000</v>
+        <v>3690000</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>250000</v>
+        <v>410000</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>62500</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7">
         <f>D5+E5+F5</f>
@@ -1370,25 +1370,25 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>05000</t>
+          <t>06000</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Structural Steel &amp; Metals</t>
+          <t>Rough Carpentry &amp; Framing</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>3600000</v>
+        <v>3800000</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>3240000</v>
+        <v>2280000</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>360000</v>
+        <v>570000</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="G6" s="7">
         <f>D6+E6+F6</f>
@@ -1406,25 +1406,25 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>06000</t>
+          <t>07000</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Rough Carpentry &amp; Framing</t>
+          <t>Thermal &amp; Moisture Protection</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>4200000</v>
+        <v>2200000</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>2520000</v>
+        <v>880000</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>630000</v>
+        <v>440000</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>210000</v>
+        <v>110000</v>
       </c>
       <c r="G7" s="7">
         <f>D7+E7+F7</f>
@@ -1442,25 +1442,25 @@
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>07000</t>
+          <t>08000</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Thermal &amp; Moisture Protection</t>
+          <t>Doors, Windows &amp; Glazing</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>2400000</v>
+        <v>2600000</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>960000</v>
+        <v>520000</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>480000</v>
+        <v>390000</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>120000</v>
+        <v>260000</v>
       </c>
       <c r="G8" s="7">
         <f>D8+E8+F8</f>
@@ -1478,25 +1478,25 @@
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>08000</t>
+          <t>09000</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Doors, Windows &amp; Glazing</t>
+          <t>Finishes (Drywall, Paint, Flooring, Tile)</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>2800000</v>
+        <v>4500000</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>560000</v>
+        <v>450000</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>420000</v>
+        <v>675000</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>280000</v>
+        <v>225000</v>
       </c>
       <c r="G9" s="7">
         <f>D9+E9+F9</f>
@@ -1514,25 +1514,25 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>09000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Finishes (Drywall, Paint, Flooring, Tile)</t>
+          <t>Mechanical / HVAC</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>5100000</v>
+        <v>3400000</v>
       </c>
       <c r="D10" s="13" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="E10" s="13" t="n">
         <v>510000</v>
       </c>
-      <c r="E10" s="13" t="n">
-        <v>765000</v>
-      </c>
       <c r="F10" s="13" t="n">
-        <v>255000</v>
+        <v>170000</v>
       </c>
       <c r="G10" s="7">
         <f>D10+E10+F10</f>
@@ -1550,25 +1550,25 @@
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Mechanical / HVAC</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>3800000</v>
+        <v>2100000</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1520000</v>
+        <v>1050000</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>570000</v>
+        <v>315000</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="7">
         <f>D11+E11+F11</f>
@@ -1586,25 +1586,25 @@
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>2350000</v>
+        <v>2800000</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1175000</v>
+        <v>1120000</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>352500</v>
+        <v>420000</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="G12" s="7">
         <f>D12+E12+F12</f>
@@ -1622,25 +1622,25 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>3100000</v>
+        <v>950000</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1240000</v>
+        <v>285000</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>465000</v>
+        <v>142500</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>155000</v>
+        <v>0</v>
       </c>
       <c r="G13" s="7">
         <f>D13+E13+F13</f>
@@ -1658,22 +1658,22 @@
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Exterior Improvements &amp; Landscaping</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1050000</v>
+        <v>1200000</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>315000</v>
+        <v>0</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>157500</v>
+        <v>0</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>0</v>
@@ -1692,60 +1692,39 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>26000</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Elevator Installation</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>850000</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>170000</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>127500</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>85000</v>
-      </c>
-      <c r="G15" s="7">
-        <f>D15+E15+F15</f>
-        <v/>
-      </c>
-      <c r="H15" s="19">
-        <f>IF(C15=0,0,G15/C15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="7">
-        <f>C15-G15</f>
-        <v/>
-      </c>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SOFT COSTS</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>32000</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Exterior Improvements &amp; Landscaping</t>
+          <t>Architecture &amp; Engineering</t>
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1350000</v>
+        <v>1800000</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>0</v>
+        <v>1620000</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>0</v>
@@ -1764,39 +1743,60 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SOFT COSTS</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>S-02</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Permits &amp; Impact Fees</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>950000</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>950000</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7">
+        <f>D17+E17+F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="19">
+        <f>IF(C17=0,0,G17/C17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="7">
+        <f>C17-G17</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Architecture &amp; Engineering</t>
+          <t>Legal &amp; Title</t>
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>2350000</v>
+        <v>350000</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>2115000</v>
+        <v>280000</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>117500</v>
+        <v>35000</v>
       </c>
       <c r="F18" s="13" t="n">
         <v>0</v>
@@ -1817,22 +1817,22 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>S-02</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Permits &amp; Impact Fees</t>
+          <t>Builder's Risk Insurance</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1400000</v>
+        <v>425000</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1400000</v>
+        <v>297500</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>0</v>
+        <v>42500</v>
       </c>
       <c r="F19" s="13" t="n">
         <v>0</v>
@@ -1851,60 +1851,39 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>S-03</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Legal &amp; Title</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="n">
-        <v>380000</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <v>304000</v>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>38000</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7">
-        <f>D20+E20+F20</f>
-        <v/>
-      </c>
-      <c r="H20" s="19">
-        <f>IF(C20=0,0,G20/C20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="7">
-        <f>C20-G20</f>
-        <v/>
-      </c>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>FINANCING COSTS</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Builder's Risk Insurance</t>
+          <t>Loan Origination &amp; Fees</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>310000</v>
+        <v>575000</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>217000</v>
+        <v>575000</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>0</v>
@@ -1923,118 +1902,139 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>FINANCING COSTS</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Loan Origination &amp; Fees</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>442000</v>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>442000</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7">
-        <f>D23+E23+F23</f>
-        <v/>
-      </c>
-      <c r="H23" s="19">
-        <f>IF(C23=0,0,G23/C23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="7">
-        <f>C23-G23</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Capitalized Interest</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>1020000</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>121500</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7">
+        <f>D22+E22+F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="19">
+        <f>IF(C22=0,0,G22/C22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="7">
+        <f>C22-G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="6" customHeight="1"/>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>F-02</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Capitalized Interest</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>2020000</v>
-      </c>
-      <c r="D24" s="13" t="n">
-        <v>1212000</v>
-      </c>
-      <c r="E24" s="13" t="n">
-        <v>141750</v>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7">
-        <f>D24+E24+F24</f>
-        <v/>
-      </c>
-      <c r="H24" s="19">
+      <c r="A24" s="20" t="inlineStr"/>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>HARD COSTS SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C24" s="14">
+        <f>C3+C4+C5+C6+C7+C8+C9+C10+C11+C12+C13+C14</f>
+        <v/>
+      </c>
+      <c r="D24" s="14">
+        <f>D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14</f>
+        <v/>
+      </c>
+      <c r="E24" s="14">
+        <f>E3+E4+E5+E6+E7+E8+E9+E10+E11+E12+E13+E14</f>
+        <v/>
+      </c>
+      <c r="F24" s="14">
+        <f>F3+F4+F5+F6+F7+F8+F9+F10+F11+F12+F13+F14</f>
+        <v/>
+      </c>
+      <c r="G24" s="14">
+        <f>G3+G4+G5+G6+G7+G8+G9+G10+G11+G12+G13+G14</f>
+        <v/>
+      </c>
+      <c r="H24" s="22">
         <f>IF(C24=0,0,G24/C24)</f>
         <v/>
       </c>
-      <c r="I24" s="7">
-        <f>C24-G24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="6" customHeight="1"/>
+      <c r="I24" s="14">
+        <f>I3+I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr"/>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>SOFT COSTS SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C25" s="14">
+        <f>C16+C17+C18+C19</f>
+        <v/>
+      </c>
+      <c r="D25" s="14">
+        <f>D16+D17+D18+D19</f>
+        <v/>
+      </c>
+      <c r="E25" s="14">
+        <f>E16+E17+E18+E19</f>
+        <v/>
+      </c>
+      <c r="F25" s="14">
+        <f>F16+F17+F18+F19</f>
+        <v/>
+      </c>
+      <c r="G25" s="14">
+        <f>G16+G17+G18+G19</f>
+        <v/>
+      </c>
+      <c r="H25" s="22">
+        <f>IF(C25=0,0,G25/C25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="14">
+        <f>I16+I17+I18+I19</f>
+        <v/>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="20" t="inlineStr"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>HARD COSTS SUBTOTAL</t>
+          <t>FINANCING COSTS SUBTOTAL</t>
         </is>
       </c>
       <c r="C26" s="14">
-        <f>C3+C4+C5+C6+C7+C8+C9+C10+C11+C12+C13+C14+C15+C16</f>
+        <f>C21+C22</f>
         <v/>
       </c>
       <c r="D26" s="14">
-        <f>D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
+        <f>D21+D22</f>
         <v/>
       </c>
       <c r="E26" s="14">
-        <f>E3+E4+E5+E6+E7+E8+E9+E10+E11+E12+E13+E14+E15+E16</f>
+        <f>E21+E22</f>
         <v/>
       </c>
       <c r="F26" s="14">
-        <f>F3+F4+F5+F6+F7+F8+F9+F10+F11+F12+F13+F14+F15+F16</f>
+        <f>F21+F22</f>
         <v/>
       </c>
       <c r="G26" s="14">
-        <f>G3+G4+G5+G6+G7+G8+G9+G10+G11+G12+G13+G14+G15+G16</f>
+        <f>G21+G22</f>
         <v/>
       </c>
       <c r="H26" s="22">
@@ -2042,121 +2042,49 @@
         <v/>
       </c>
       <c r="I26" s="14">
-        <f>I3+I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="20" t="inlineStr"/>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>SOFT COSTS SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C27" s="14">
-        <f>C18+C19+C20+C21</f>
-        <v/>
-      </c>
-      <c r="D27" s="14">
-        <f>D18+D19+D20+D21</f>
-        <v/>
-      </c>
-      <c r="E27" s="14">
-        <f>E18+E19+E20+E21</f>
-        <v/>
-      </c>
-      <c r="F27" s="14">
-        <f>F18+F19+F20+F21</f>
-        <v/>
-      </c>
-      <c r="G27" s="14">
-        <f>G18+G19+G20+G21</f>
-        <v/>
-      </c>
-      <c r="H27" s="22">
-        <f>IF(C27=0,0,G27/C27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="14">
-        <f>I18+I19+I20+I21</f>
-        <v/>
-      </c>
-    </row>
+        <f>I21+I22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="6" customHeight="1"/>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr"/>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>FINANCING COSTS SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="C28" s="14">
-        <f>C23+C24</f>
-        <v/>
-      </c>
-      <c r="D28" s="14">
-        <f>D23+D24</f>
-        <v/>
-      </c>
-      <c r="E28" s="14">
-        <f>E23+E24</f>
-        <v/>
-      </c>
-      <c r="F28" s="14">
-        <f>F23+F24</f>
-        <v/>
-      </c>
-      <c r="G28" s="14">
-        <f>G23+G24</f>
-        <v/>
-      </c>
-      <c r="H28" s="22">
+      <c r="A28" s="23" t="inlineStr"/>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL</t>
+        </is>
+      </c>
+      <c r="C28" s="25">
+        <f>C24+C25+C26</f>
+        <v/>
+      </c>
+      <c r="D28" s="25">
+        <f>D24+D25+D26</f>
+        <v/>
+      </c>
+      <c r="E28" s="25">
+        <f>E24+E25+E26</f>
+        <v/>
+      </c>
+      <c r="F28" s="25">
+        <f>F24+F25+F26</f>
+        <v/>
+      </c>
+      <c r="G28" s="25">
+        <f>G24+G25+G26</f>
+        <v/>
+      </c>
+      <c r="H28" s="26">
         <f>IF(C28=0,0,G28/C28)</f>
         <v/>
       </c>
-      <c r="I28" s="14">
-        <f>I23+I24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="6" customHeight="1"/>
-    <row r="30">
-      <c r="A30" s="23" t="inlineStr"/>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>GRAND TOTAL</t>
-        </is>
-      </c>
-      <c r="C30" s="25">
-        <f>C26+C27+C28</f>
-        <v/>
-      </c>
-      <c r="D30" s="25">
-        <f>D26+D27+D28</f>
-        <v/>
-      </c>
-      <c r="E30" s="25">
-        <f>E26+E27+E28</f>
-        <v/>
-      </c>
-      <c r="F30" s="25">
-        <f>F26+F27+F28</f>
-        <v/>
-      </c>
-      <c r="G30" s="25">
-        <f>G26+G27+G28</f>
-        <v/>
-      </c>
-      <c r="H30" s="26">
-        <f>IF(C30=0,0,G30/C30)</f>
-        <v/>
-      </c>
-      <c r="I30" s="25">
-        <f>I26+I27+I28</f>
+      <c r="I28" s="25">
+        <f>I24+I25+I26</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H24">
+  <conditionalFormatting sqref="H2:H22">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.999</formula>
     </cfRule>
@@ -2176,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2240,21 +2168,21 @@
       </c>
       <c r="B2" s="18" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Enhanced lobby finishes and upgraded amenity package per ownership directive</t>
+          <t>Upgraded elevator cab finishes per owner request</t>
         </is>
       </c>
       <c r="E2" s="13" t="n">
-        <v>215000</v>
+        <v>185000</v>
       </c>
       <c r="F2" s="7">
         <f>E2</f>
@@ -2275,28 +2203,28 @@
       </c>
       <c r="B3" s="18" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Dewatering system for unexpected high water table at podium level</t>
+          <t>Rock removal — unforeseen subsurface conditions at Building C</t>
         </is>
       </c>
       <c r="E3" s="13" t="n">
-        <v>287000</v>
+        <v>342000</v>
       </c>
       <c r="F3" s="7">
         <f>F2+E3</f>
         <v/>
       </c>
       <c r="G3" s="27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H3" s="18" t="inlineStr">
         <is>
@@ -2310,28 +2238,28 @@
       </c>
       <c r="B4" s="18" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Upgraded fire alarm panel to addressable system per city code revision</t>
+          <t>Structural steel reinforcement per revised wind load calcs</t>
         </is>
       </c>
       <c r="E4" s="13" t="n">
-        <v>94000</v>
+        <v>128000</v>
       </c>
       <c r="F4" s="7">
         <f>F3+E4</f>
         <v/>
       </c>
       <c r="G4" s="27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4" s="18" t="inlineStr">
         <is>
@@ -2339,59 +2267,28 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>EV charging infrastructure for 40 parking spaces per revised ESG commitment</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>168000</v>
-      </c>
-      <c r="F5" s="7">
-        <f>F4+E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="6" customHeight="1"/>
-    <row r="7">
-      <c r="B7" s="24" t="inlineStr">
+    <row r="5" ht="6" customHeight="1"/>
+    <row r="6">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="E7" s="25">
-        <f>SUM(E2:E5)</f>
-        <v/>
-      </c>
-      <c r="F7" s="25">
-        <f>F5</f>
-        <v/>
-      </c>
-      <c r="G7" s="28">
-        <f>SUM(G2:G5)</f>
+      <c r="E6" s="25">
+        <f>SUM(E2:E4)</f>
+        <v/>
+      </c>
+      <c r="F6" s="25">
+        <f>F4</f>
+        <v/>
+      </c>
+      <c r="G6" s="28">
+        <f>SUM(G2:G4)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H4">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"approved"</formula>
     </cfRule>
@@ -2414,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2511,7 +2408,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>2450000</v>
+        <v>2850000</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>0</v>
@@ -2521,7 +2418,7 @@
         <v/>
       </c>
       <c r="E3" s="13" t="n">
-        <v>2450000</v>
+        <v>2850000</v>
       </c>
       <c r="F3" s="13" t="n">
         <v>0</v>
@@ -2550,7 +2447,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>4800000</v>
+        <v>5200000</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>0</v>
@@ -2560,7 +2457,7 @@
         <v/>
       </c>
       <c r="E4" s="13" t="n">
-        <v>4800000</v>
+        <v>5200000</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>0</v>
@@ -2585,11 +2482,11 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Masonry</t>
+          <t>Structural Steel &amp; Metals</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1250000</v>
+        <v>4100000</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>0</v>
@@ -2599,10 +2496,10 @@
         <v/>
       </c>
       <c r="E5" s="13" t="n">
-        <v>875000</v>
+        <v>3690000</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>312500</v>
+        <v>410000</v>
       </c>
       <c r="G5" s="7">
         <f>E5+F5</f>
@@ -2624,11 +2521,11 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Structural Steel &amp; Metals</t>
+          <t>Rough Carpentry &amp; Framing</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>3600000</v>
+        <v>3800000</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>0</v>
@@ -2638,10 +2535,10 @@
         <v/>
       </c>
       <c r="E6" s="13" t="n">
-        <v>3240000</v>
+        <v>2280000</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>360000</v>
+        <v>760000</v>
       </c>
       <c r="G6" s="7">
         <f>E6+F6</f>
@@ -2663,11 +2560,11 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Rough Carpentry &amp; Framing</t>
+          <t>Thermal &amp; Moisture Protection</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>4200000</v>
+        <v>2200000</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>0</v>
@@ -2677,10 +2574,10 @@
         <v/>
       </c>
       <c r="E7" s="13" t="n">
-        <v>2520000</v>
+        <v>880000</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>840000</v>
+        <v>550000</v>
       </c>
       <c r="G7" s="7">
         <f>E7+F7</f>
@@ -2702,11 +2599,11 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Thermal &amp; Moisture Protection</t>
+          <t>Doors, Windows &amp; Glazing</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>2400000</v>
+        <v>2600000</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>0</v>
@@ -2716,10 +2613,10 @@
         <v/>
       </c>
       <c r="E8" s="13" t="n">
-        <v>960000</v>
+        <v>520000</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>600000</v>
+        <v>650000</v>
       </c>
       <c r="G8" s="7">
         <f>E8+F8</f>
@@ -2741,11 +2638,11 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Doors, Windows &amp; Glazing</t>
+          <t>Finishes (Drywall, Paint, Flooring, Tile)</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>2800000</v>
+        <v>4500000</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>0</v>
@@ -2755,10 +2652,10 @@
         <v/>
       </c>
       <c r="E9" s="13" t="n">
-        <v>560000</v>
+        <v>450000</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>700000</v>
+        <v>900000</v>
       </c>
       <c r="G9" s="7">
         <f>E9+F9</f>
@@ -2780,11 +2677,11 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Finishes (Drywall, Paint, Flooring, Tile)</t>
+          <t>Mechanical / HVAC</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>5100000</v>
+        <v>3400000</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>0</v>
@@ -2794,10 +2691,10 @@
         <v/>
       </c>
       <c r="E10" s="13" t="n">
-        <v>510000</v>
+        <v>1360000</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1020000</v>
+        <v>680000</v>
       </c>
       <c r="G10" s="7">
         <f>E10+F10</f>
@@ -2819,11 +2716,11 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Mechanical / HVAC</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>3800000</v>
+        <v>2100000</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>0</v>
@@ -2833,10 +2730,10 @@
         <v/>
       </c>
       <c r="E11" s="13" t="n">
-        <v>1520000</v>
+        <v>1050000</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>760000</v>
+        <v>315000</v>
       </c>
       <c r="G11" s="7">
         <f>E11+F11</f>
@@ -2858,11 +2755,11 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>2350000</v>
+        <v>2800000</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>0</v>
@@ -2872,10 +2769,10 @@
         <v/>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1175000</v>
+        <v>1120000</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>352500</v>
+        <v>560000</v>
       </c>
       <c r="G12" s="7">
         <f>E12+F12</f>
@@ -2897,11 +2794,11 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>3100000</v>
+        <v>950000</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>0</v>
@@ -2911,10 +2808,10 @@
         <v/>
       </c>
       <c r="E13" s="13" t="n">
-        <v>1240000</v>
+        <v>285000</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>620000</v>
+        <v>142500</v>
       </c>
       <c r="G13" s="7">
         <f>E13+F13</f>
@@ -2936,11 +2833,11 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Exterior Improvements &amp; Landscaping</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1050000</v>
+        <v>1200000</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>0</v>
@@ -2950,10 +2847,10 @@
         <v/>
       </c>
       <c r="E14" s="13" t="n">
-        <v>315000</v>
+        <v>0</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>157500</v>
+        <v>0</v>
       </c>
       <c r="G14" s="7">
         <f>E14+F14</f>
@@ -2973,52 +2870,29 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Elevator Installation</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>850000</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7">
-        <f>B15+C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>170000</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>212500</v>
-      </c>
-      <c r="G15" s="7">
-        <f>E15+F15</f>
-        <v/>
-      </c>
-      <c r="H15" s="7">
-        <f>D15-G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="13">
-        <f>D15</f>
-        <v/>
-      </c>
-      <c r="J15" s="7">
-        <f>I15-D15</f>
-        <v/>
-      </c>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SOFT COSTS</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Exterior Improvements &amp; Landscaping</t>
+          <t>Architecture &amp; Engineering</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>1350000</v>
+        <v>1800000</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>0</v>
@@ -3028,10 +2902,10 @@
         <v/>
       </c>
       <c r="E16" s="13" t="n">
-        <v>0</v>
+        <v>1620000</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="G16" s="7">
         <f>E16+F16</f>
@@ -3051,29 +2925,52 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SOFT COSTS</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Permits &amp; Impact Fees</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>950000</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7">
+        <f>B17+C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>950000</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7">
+        <f>E17+F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="7">
+        <f>D17-G17</f>
+        <v/>
+      </c>
+      <c r="I17" s="13">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="J17" s="7">
+        <f>I17-D17</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Architecture &amp; Engineering</t>
+          <t>Legal &amp; Title</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>2350000</v>
+        <v>350000</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>0</v>
@@ -3083,10 +2980,10 @@
         <v/>
       </c>
       <c r="E18" s="13" t="n">
-        <v>2115000</v>
+        <v>280000</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>117500</v>
+        <v>35000</v>
       </c>
       <c r="G18" s="7">
         <f>E18+F18</f>
@@ -3108,11 +3005,11 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Permits &amp; Impact Fees</t>
+          <t>Builder's Risk Insurance</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1400000</v>
+        <v>425000</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>0</v>
@@ -3122,10 +3019,10 @@
         <v/>
       </c>
       <c r="E19" s="13" t="n">
-        <v>1400000</v>
+        <v>297500</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0</v>
+        <v>42500</v>
       </c>
       <c r="G19" s="7">
         <f>E19+F19</f>
@@ -3145,52 +3042,29 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Legal &amp; Title</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>380000</v>
-      </c>
-      <c r="C20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7">
-        <f>B20+C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>304000</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>38000</v>
-      </c>
-      <c r="G20" s="7">
-        <f>E20+F20</f>
-        <v/>
-      </c>
-      <c r="H20" s="7">
-        <f>D20-G20</f>
-        <v/>
-      </c>
-      <c r="I20" s="13">
-        <f>D20</f>
-        <v/>
-      </c>
-      <c r="J20" s="7">
-        <f>I20-D20</f>
-        <v/>
-      </c>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>FINANCING COSTS</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Builder's Risk Insurance</t>
+          <t>Loan Origination &amp; Fees</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>310000</v>
+        <v>575000</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0</v>
@@ -3200,10 +3074,10 @@
         <v/>
       </c>
       <c r="E21" s="13" t="n">
-        <v>217000</v>
+        <v>575000</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="G21" s="7">
         <f>E21+F21</f>
@@ -3223,112 +3097,143 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>FINANCING COSTS</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Loan Origination &amp; Fees</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="n">
-        <v>442000</v>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7">
-        <f>B23+C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>442000</v>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7">
-        <f>E23+F23</f>
-        <v/>
-      </c>
-      <c r="H23" s="7">
-        <f>D23-G23</f>
-        <v/>
-      </c>
-      <c r="I23" s="13">
-        <f>D23</f>
-        <v/>
-      </c>
-      <c r="J23" s="7">
-        <f>I23-D23</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Capitalized Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7">
+        <f>B22+C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>1020000</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>121500</v>
+      </c>
+      <c r="G22" s="7">
+        <f>E22+F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="7">
+        <f>D22-G22</f>
+        <v/>
+      </c>
+      <c r="I22" s="13">
+        <f>D22</f>
+        <v/>
+      </c>
+      <c r="J22" s="7">
+        <f>I22-D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="6" customHeight="1"/>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Capitalized Interest</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="n">
-        <v>2020000</v>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>HARD COSTS SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B24" s="14">
+        <f>B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14</f>
+        <v/>
+      </c>
+      <c r="C24" s="14">
+        <f>C3+C4+C5+C6+C7+C8+C9+C10+C11+C12+C13+C14</f>
+        <v/>
+      </c>
+      <c r="D24" s="14">
         <f>B24+C24</f>
         <v/>
       </c>
-      <c r="E24" s="13" t="n">
-        <v>1212000</v>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>141750</v>
-      </c>
-      <c r="G24" s="7">
+      <c r="E24" s="14">
+        <f>E3+E4+E5+E6+E7+E8+E9+E10+E11+E12+E13+E14</f>
+        <v/>
+      </c>
+      <c r="F24" s="14">
+        <f>F3+F4+F5+F6+F7+F8+F9+F10+F11+F12+F13+F14</f>
+        <v/>
+      </c>
+      <c r="G24" s="14">
         <f>E24+F24</f>
         <v/>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="14">
         <f>D24-G24</f>
         <v/>
       </c>
-      <c r="I24" s="13">
-        <f>D24</f>
-        <v/>
-      </c>
-      <c r="J24" s="7">
+      <c r="I24" s="14">
+        <f>I3+I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14</f>
+        <v/>
+      </c>
+      <c r="J24" s="14">
         <f>I24-D24</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="6" customHeight="1"/>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>SOFT COSTS SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B25" s="14">
+        <f>B16+B17+B18+B19</f>
+        <v/>
+      </c>
+      <c r="C25" s="14">
+        <f>C16+C17+C18+C19</f>
+        <v/>
+      </c>
+      <c r="D25" s="14">
+        <f>B25+C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="14">
+        <f>E16+E17+E18+E19</f>
+        <v/>
+      </c>
+      <c r="F25" s="14">
+        <f>F16+F17+F18+F19</f>
+        <v/>
+      </c>
+      <c r="G25" s="14">
+        <f>E25+F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="14">
+        <f>D25-G25</f>
+        <v/>
+      </c>
+      <c r="I25" s="14">
+        <f>I16+I17+I18+I19</f>
+        <v/>
+      </c>
+      <c r="J25" s="14">
+        <f>I25-D25</f>
+        <v/>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>HARD COSTS SUBTOTAL</t>
+          <t>FINANCING COSTS SUBTOTAL</t>
         </is>
       </c>
       <c r="B26" s="14">
-        <f>B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16</f>
+        <f>B21+B22</f>
         <v/>
       </c>
       <c r="C26" s="14">
-        <f>C3+C4+C5+C6+C7+C8+C9+C10+C11+C12+C13+C14+C15+C16</f>
+        <f>C21+C22</f>
         <v/>
       </c>
       <c r="D26" s="14">
@@ -3336,11 +3241,11 @@
         <v/>
       </c>
       <c r="E26" s="14">
-        <f>E3+E4+E5+E6+E7+E8+E9+E10+E11+E12+E13+E14+E15+E16</f>
+        <f>E21+E22</f>
         <v/>
       </c>
       <c r="F26" s="14">
-        <f>F3+F4+F5+F6+F7+F8+F9+F10+F11+F12+F13+F14+F15+F16</f>
+        <f>F21+F22</f>
         <v/>
       </c>
       <c r="G26" s="14">
@@ -3352,7 +3257,7 @@
         <v/>
       </c>
       <c r="I26" s="14">
-        <f>I3+I4+I5+I6+I7+I8+I9+I10+I11+I12+I13+I14+I15+I16</f>
+        <f>I21+I22</f>
         <v/>
       </c>
       <c r="J26" s="14">
@@ -3360,138 +3265,52 @@
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>SOFT COSTS SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B27" s="14">
-        <f>B18+B19+B20+B21</f>
-        <v/>
-      </c>
-      <c r="C27" s="14">
-        <f>C18+C19+C20+C21</f>
-        <v/>
-      </c>
-      <c r="D27" s="14">
-        <f>B27+C27</f>
-        <v/>
-      </c>
-      <c r="E27" s="14">
-        <f>E18+E19+E20+E21</f>
-        <v/>
-      </c>
-      <c r="F27" s="14">
-        <f>F18+F19+F20+F21</f>
-        <v/>
-      </c>
-      <c r="G27" s="14">
-        <f>E27+F27</f>
-        <v/>
-      </c>
-      <c r="H27" s="14">
-        <f>D27-G27</f>
-        <v/>
-      </c>
-      <c r="I27" s="14">
-        <f>I18+I19+I20+I21</f>
-        <v/>
-      </c>
-      <c r="J27" s="14">
-        <f>I27-D27</f>
-        <v/>
-      </c>
-    </row>
+    <row r="27" ht="6" customHeight="1"/>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>FINANCING COSTS SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B28" s="14">
-        <f>B23+B24</f>
-        <v/>
-      </c>
-      <c r="C28" s="14">
-        <f>C23+C24</f>
-        <v/>
-      </c>
-      <c r="D28" s="14">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>TOTAL PROJECT BUDGET</t>
+        </is>
+      </c>
+      <c r="B28" s="25">
+        <f>B24+B25+B26</f>
+        <v/>
+      </c>
+      <c r="C28" s="25">
+        <f>C24+C25+C26</f>
+        <v/>
+      </c>
+      <c r="D28" s="25">
         <f>B28+C28</f>
         <v/>
       </c>
-      <c r="E28" s="14">
-        <f>E23+E24</f>
-        <v/>
-      </c>
-      <c r="F28" s="14">
-        <f>F23+F24</f>
-        <v/>
-      </c>
-      <c r="G28" s="14">
+      <c r="E28" s="25">
+        <f>E24+E25+E26</f>
+        <v/>
+      </c>
+      <c r="F28" s="25">
+        <f>F24+F25+F26</f>
+        <v/>
+      </c>
+      <c r="G28" s="25">
         <f>E28+F28</f>
         <v/>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="25">
         <f>D28-G28</f>
         <v/>
       </c>
-      <c r="I28" s="14">
-        <f>I23+I24</f>
-        <v/>
-      </c>
-      <c r="J28" s="14">
+      <c r="I28" s="25">
+        <f>I24+I25+I26</f>
+        <v/>
+      </c>
+      <c r="J28" s="25">
         <f>I28-D28</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="6" customHeight="1"/>
-    <row r="30">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>TOTAL PROJECT BUDGET</t>
-        </is>
-      </c>
-      <c r="B30" s="25">
-        <f>B26+B27+B28</f>
-        <v/>
-      </c>
-      <c r="C30" s="25">
-        <f>C26+C27+C28</f>
-        <v/>
-      </c>
-      <c r="D30" s="25">
-        <f>B30+C30</f>
-        <v/>
-      </c>
-      <c r="E30" s="25">
-        <f>E26+E27+E28</f>
-        <v/>
-      </c>
-      <c r="F30" s="25">
-        <f>F26+F27+F28</f>
-        <v/>
-      </c>
-      <c r="G30" s="25">
-        <f>E30+F30</f>
-        <v/>
-      </c>
-      <c r="H30" s="25">
-        <f>D30-G30</f>
-        <v/>
-      </c>
-      <c r="I30" s="25">
-        <f>I26+I27+I28</f>
-        <v/>
-      </c>
-      <c r="J30" s="25">
-        <f>I30-D30</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="J3:J24">
+  <conditionalFormatting sqref="J3:J22">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -3511,7 +3330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3587,7 +3406,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Central Ohio Earthworks</t>
+          <t>Great Lakes Excavating</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -3596,10 +3415,10 @@
         </is>
       </c>
       <c r="C2" s="13" t="n">
-        <v>2450000</v>
+        <v>2850000</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>2205000</v>
+        <v>2565000</v>
       </c>
       <c r="E2" s="13" t="n">
         <v>0</v>
@@ -3632,19 +3451,19 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Buckeye Concrete Inc</t>
+          <t>Motor City Concrete</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Concrete &amp; Foundations</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>4800000</v>
+        <v>5200000</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>4320000</v>
+        <v>4680000</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>0</v>
@@ -3665,7 +3484,7 @@
       </c>
       <c r="I3" s="18" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -3677,22 +3496,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Capital City Masonry</t>
+          <t>Ironworkers Local 25 Steel</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Masonry</t>
+          <t>Structural Steel</t>
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1250000</v>
+        <v>4100000</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>787500</v>
+        <v>3321000</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>281250</v>
+        <v>369000</v>
       </c>
       <c r="F4" s="7">
         <f>C4-D4-E4</f>
@@ -3718,22 +3537,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Midwest Steel Erectors</t>
+          <t>Midwest Framing Corp</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Rough Carpentry</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>3600000</v>
+        <v>3800000</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>2916000</v>
+        <v>2052000</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>324000</v>
+        <v>684000</v>
       </c>
       <c r="F5" s="7">
         <f>C5-D5-E5</f>
@@ -3759,22 +3578,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Scioto Framing Corp</t>
+          <t>Barrier Systems Inc</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Rough Carpentry</t>
+          <t>Waterproofing &amp; Insulation</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>4200000</v>
+        <v>2200000</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>2268000</v>
+        <v>792000</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>756000</v>
+        <v>495000</v>
       </c>
       <c r="F6" s="7">
         <f>C6-D6-E6</f>
@@ -3787,7 +3606,7 @@
       </c>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr">
@@ -3795,27 +3614,31 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Unconditional for Draw 6 still pending</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Ohio Weatherproofing LLC</t>
+          <t>Wolverine Glass &amp; Glazing</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Waterproofing &amp; Insulation</t>
+          <t>Windows &amp; Glazing</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>2400000</v>
+        <v>2600000</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>864000</v>
+        <v>468000</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>540000</v>
+        <v>585000</v>
       </c>
       <c r="F7" s="7">
         <f>C7-D7-E7</f>
@@ -3828,7 +3651,7 @@
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="I7" s="18" t="inlineStr">
@@ -3836,31 +3659,27 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Unconditional for Draw 7 still pending</t>
-        </is>
-      </c>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Columbus Glass &amp; Curtainwall</t>
+          <t>Elite Interior Finishes</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Windows &amp; Glazing</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>2800000</v>
+        <v>4500000</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>504000</v>
+        <v>405000</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>630000</v>
+        <v>810000</v>
       </c>
       <c r="F8" s="7">
         <f>C8-D8-E8</f>
@@ -3868,40 +3687,40 @@
       </c>
       <c r="G8" s="18" t="inlineStr">
         <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="I8" s="18" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Conditional waiver requested — awaiting return</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Premier Interior Solutions</t>
+          <t>Comfort Mechanical</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>5100000</v>
+        <v>3400000</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>459000</v>
+        <v>1224000</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>918000</v>
+        <v>612000</v>
       </c>
       <c r="F9" s="7">
         <f>C9-D9-E9</f>
@@ -3909,7 +3728,7 @@
       </c>
       <c r="G9" s="18" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr">
@@ -3917,32 +3736,32 @@
           <t>Received</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Conditional waiver requested — awaiting return</t>
-        </is>
-      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Heartland Mechanical</t>
+          <t>Allied Plumbing Services</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Plumbing</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>3800000</v>
+        <v>2100000</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1368000</v>
+        <v>945000</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>684000</v>
+        <v>283500</v>
       </c>
       <c r="F10" s="7">
         <f>C10-D10-E10</f>
@@ -3960,7 +3779,7 @@
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
@@ -3968,22 +3787,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Olentangy Plumbing Services</t>
+          <t>PowerLine Electric</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>2350000</v>
+        <v>2800000</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1057500</v>
+        <v>1008000</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>317250</v>
+        <v>504000</v>
       </c>
       <c r="F11" s="7">
         <f>C11-D11-E11</f>
@@ -3996,35 +3815,39 @@
       </c>
       <c r="H11" s="18" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Unconditional for Draw 6 missing — follow up</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Apex Electrical Contractors</t>
+          <t>FireGuard Sprinkler</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Fire Protection</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>3100000</v>
+        <v>950000</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1116000</v>
+        <v>256500</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>558000</v>
+        <v>128250</v>
       </c>
       <c r="F12" s="7">
         <f>C12-D12-E12</f>
@@ -4037,39 +3860,35 @@
       </c>
       <c r="H12" s="18" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>Unconditional for Draw 7 missing — follow up</t>
-        </is>
-      </c>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Buckeye Fire Protection</t>
+          <t>GreenScape Landscaping</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Fire Protection</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1050000</v>
+        <v>1200000</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>283500</v>
+        <v>0</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>141750</v>
+        <v>0</v>
       </c>
       <c r="F13" s="7">
         <f>C13-D13-E13</f>
@@ -4077,224 +3896,142 @@
       </c>
       <c r="G13" s="18" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H13" s="18" t="inlineStr">
         <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Schindler Elevator Corp</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Elevators</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>850000</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>153000</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>191250</v>
-      </c>
-      <c r="F14" s="7">
-        <f>C14-D14-E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
-    </row>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Not yet mobilized</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Greenview Landscaping</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Landscaping &amp; Exterior</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7">
-        <f>C15-D15-E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Not yet mobilized</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="6" customHeight="1"/>
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C15" s="25">
+        <f>SUM(C2:C13)</f>
+        <v/>
+      </c>
+      <c r="D15" s="25">
+        <f>SUM(D2:D13)</f>
+        <v/>
+      </c>
+      <c r="E15" s="25">
+        <f>SUM(E2:E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="25">
+        <f>SUM(F2:F13)</f>
+        <v/>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>TOTALS</t>
-        </is>
-      </c>
-      <c r="C17" s="25">
-        <f>SUM(C2:C15)</f>
-        <v/>
-      </c>
-      <c r="D17" s="25">
-        <f>SUM(D2:D15)</f>
-        <v/>
-      </c>
-      <c r="E17" s="25">
-        <f>SUM(E2:E15)</f>
-        <v/>
-      </c>
-      <c r="F17" s="25">
-        <f>SUM(F2:F15)</f>
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>COMPLIANCE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Active Subcontractors</t>
+        </is>
+      </c>
+      <c r="B18" s="30">
+        <f>COUNTIF(E2:E13,"&gt;0")+COUNTIF(D2:D13,"&gt;0")-COUNTIFS(E2:E13,"&gt;0",D2:D13,"&gt;0")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
-        <is>
-          <t>COMPLIANCE SUMMARY</t>
-        </is>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Conditional Waivers — Received</t>
+        </is>
+      </c>
+      <c r="B19" s="30">
+        <f>COUNTIF(G2:G13,"Received")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Active Subcontractors</t>
+          <t>Conditional Waivers — Pending</t>
         </is>
       </c>
       <c r="B20" s="30">
-        <f>COUNTIF(E2:E15,"&gt;0")+COUNTIF(D2:D15,"&gt;0")-COUNTIFS(E2:E15,"&gt;0",D2:D15,"&gt;0")</f>
+        <f>COUNTIF(G2:G13,"Pending")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Conditional Waivers — Received</t>
+          <t>Conditional Waivers — Missing</t>
         </is>
       </c>
       <c r="B21" s="30">
-        <f>COUNTIF(G2:G15,"Received")</f>
+        <f>COUNTIF(G2:G13,"Missing")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Conditional Waivers — Pending</t>
+          <t>Unconditional Waivers — Received</t>
         </is>
       </c>
       <c r="B22" s="30">
-        <f>COUNTIF(G2:G15,"Pending")</f>
+        <f>COUNTIF(H2:H13,"Received")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Conditional Waivers — Missing</t>
+          <t>Unconditional Waivers — Pending/Missing</t>
         </is>
       </c>
       <c r="B23" s="30">
-        <f>COUNTIF(G2:G15,"Missing")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Unconditional Waivers — Received</t>
-        </is>
-      </c>
-      <c r="B24" s="30">
-        <f>COUNTIF(H2:H15,"Received")</f>
+        <f>COUNTIF(H2:H13,"Pending")+COUNTIF(H2:H13,"Missing")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Unconditional Waivers — Pending/Missing</t>
-        </is>
-      </c>
-      <c r="B25" s="30">
-        <f>COUNTIF(H2:H15,"Pending")+COUNTIF(H2:H15,"Missing")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
           <t>Conditional Compliance %</t>
         </is>
       </c>
-      <c r="B27" s="31">
-        <f>IF((COUNTIF(G2:G15,"Received")+COUNTIF(G2:G15,"Pending")+COUNTIF(G2:G15,"Missing"))=0,0,COUNTIF(G2:G15,"Received")/(COUNTIF(G2:G15,"Received")+COUNTIF(G2:G15,"Pending")+COUNTIF(G2:G15,"Missing")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="B25" s="31">
+        <f>IF((COUNTIF(G2:G13,"Received")+COUNTIF(G2:G13,"Pending")+COUNTIF(G2:G13,"Missing"))=0,0,COUNTIF(G2:G13,"Received")/(COUNTIF(G2:G13,"Received")+COUNTIF(G2:G13,"Pending")+COUNTIF(G2:G13,"Missing")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Unconditional Compliance %</t>
         </is>
       </c>
-      <c r="B28" s="31">
-        <f>IF((COUNTIF(H2:H15,"Received")+COUNTIF(H2:H15,"Pending")+COUNTIF(H2:H15,"Missing"))=0,0,COUNTIF(H2:H15,"Received")/(COUNTIF(H2:H15,"Received")+COUNTIF(H2:H15,"Pending")+COUNTIF(H2:H15,"Missing")))</f>
+      <c r="B26" s="31">
+        <f>IF((COUNTIF(H2:H13,"Received")+COUNTIF(H2:H13,"Pending")+COUNTIF(H2:H13,"Missing"))=0,0,COUNTIF(H2:H13,"Received")/(COUNTIF(H2:H13,"Received")+COUNTIF(H2:H13,"Pending")+COUNTIF(H2:H13,"Missing")))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G15">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Received"</formula>
     </cfRule>
@@ -4305,7 +4042,7 @@
       <formula>"Missing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H15">
+  <conditionalFormatting sqref="H2:H13">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
       <formula>"Received"</formula>
     </cfRule>
